--- a/data/trans_dic/P44D-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44D-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,43</t>
+          <t>0,0; 30,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,41</t>
+          <t>0,0; 30,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,08</t>
+          <t>1,73; 7,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,35</t>
+          <t>0,0; 19,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,0</t>
+          <t>1,46; 5,28</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,38</t>
+          <t>0,0; 41,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 29,81</t>
+          <t>5,57; 30,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 7,99</t>
+          <t>3,59; 11,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 28,38</t>
+          <t>3,1; 27,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 33,79</t>
+          <t>3,92; 35,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,25</t>
+          <t>2,84; 8,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 26,11</t>
+          <t>5,17; 25,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 26,05</t>
+          <t>8,15; 26,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,94</t>
+          <t>3,87; 8,92</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,34</t>
+          <t>0,0; 24,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,58</t>
+          <t>3,25; 28,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 23,02</t>
+          <t>9,77; 23,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 49,69</t>
+          <t>9,16; 47,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 39,29</t>
+          <t>5,24; 39,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 18,92</t>
+          <t>8,13; 19,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 30,56</t>
+          <t>7,96; 32,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 25,56</t>
+          <t>4,46; 24,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 18,63</t>
+          <t>10,22; 19,05</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 36,18</t>
+          <t>7,8; 38,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,72; 36,26</t>
+          <t>12,98; 35,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,06; 17,56</t>
+          <t>8,79; 17,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 43,93</t>
+          <t>10,12; 47,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 28,1</t>
+          <t>3,19; 29,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 12,18</t>
+          <t>5,74; 11,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 34,97</t>
+          <t>11,07; 36,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 30,45</t>
+          <t>12,18; 28,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,93</t>
+          <t>8,25; 13,51</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 22,96</t>
+          <t>6,58; 22,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 20,88</t>
+          <t>9,12; 20,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,61</t>
+          <t>7,54; 12,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,58</t>
+          <t>10,57; 27,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 19,58</t>
+          <t>6,02; 19,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 9,18</t>
+          <t>5,78; 9,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,57; 21,61</t>
+          <t>10,35; 21,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,88</t>
+          <t>9,02; 17,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,02</t>
+          <t>7,24; 10,04</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5843</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5538</t>
+          <t>0; 4659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5847</t>
+          <t>0; 6248</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4144</t>
+          <t>0; 5030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1517; 6914</t>
+          <t>1837; 7492</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6411</t>
+          <t>0; 5994</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2558; 9541</t>
+          <t>3043; 11025</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>17848</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11507</t>
+          <t>0; 11727</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2165; 11541</t>
+          <t>2156; 11806</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1529; 30901</t>
+          <t>5528; 17342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1136; 10312</t>
+          <t>1128; 10070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1157; 10242</t>
+          <t>1187; 10739</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3807; 11763</t>
+          <t>3981; 12239</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3379; 16927</t>
+          <t>3355; 16545</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5780; 17983</t>
+          <t>5628; 18136</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4587; 35695</t>
+          <t>11387; 26256</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25268</t>
+          <t>29114</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6967</t>
+          <t>0; 7053</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1031; 8377</t>
+          <t>1024; 8846</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10430; 24798</t>
+          <t>11634; 28530</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2895; 13618</t>
+          <t>2509; 12929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>999; 7538</t>
+          <t>1005; 7638</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5321; 13682</t>
+          <t>6919; 16343</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3852; 17123</t>
+          <t>4462; 18426</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2244; 12958</t>
+          <t>2259; 12340</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17573; 33546</t>
+          <t>20875; 38906</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24601</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>42075</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3083; 14610</t>
+          <t>3149; 15676</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7307; 20828</t>
+          <t>7455; 20467</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17338; 33621</t>
+          <t>17478; 34445</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2194; 12724</t>
+          <t>2932; 13616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1073; 9710</t>
+          <t>1104; 10091</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11403; 22203</t>
+          <t>11370; 22692</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8193; 24248</t>
+          <t>7673; 25295</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11293; 28009</t>
+          <t>11206; 26639</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31796; 52055</t>
+          <t>32755; 53631</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7959; 25874</t>
+          <t>7418; 25094</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14556; 32903</t>
+          <t>14371; 32738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21733; 82658</t>
+          <t>43276; 70065</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11935; 30070</t>
+          <t>11527; 29719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6460; 21299</t>
+          <t>6545; 21487</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27459; 44017</t>
+          <t>30610; 49095</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23433; 47920</t>
+          <t>22938; 48677</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24879; 47632</t>
+          <t>24014; 47511</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45666; 113496</t>
+          <t>79876; 110878</t>
         </is>
       </c>
     </row>
